--- a/owlcms/src/main/resources/templates/weighin/_WeighInForm_x2-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/weighin/_WeighInForm_x2-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\weighin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF17968-50AE-4609-9607-EC685769669D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A07800-3CB9-471A-B1A4-D9C46EF5D402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1815" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weigh-in" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
     <definedName name="tirage" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
     <definedName name="tirage">'Weigh-in'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
   <si>
     <t>${t.get("Competition.competitionName")} :</t>
   </si>
@@ -176,9 +176,6 @@
   </si>
   <si>
     <t>${l.lastName}, ${l.firstName}</t>
-  </si>
-  <si>
-    <t>${l.bodyWeight}</t>
   </si>
   <si>
     <t>${l.club}</t>
@@ -475,22 +472,12 @@
   </cellStyleXfs>
   <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -583,9 +570,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -612,15 +596,28 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -907,147 +904,147 @@
     <col min="2" max="2" width="5.7109375" customWidth="1"/>
     <col min="3" max="3" width="41.140625" customWidth="1"/>
     <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="6" customWidth="1"/>
-    <col min="6" max="7" width="14.28515625" style="6" customWidth="1"/>
-    <col min="8" max="10" width="12.140625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="6" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="14.28515625" style="3" customWidth="1"/>
+    <col min="8" max="10" width="12.140625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" style="3" customWidth="1"/>
     <col min="13" max="13" width="7.7109375" customWidth="1"/>
-    <col min="14" max="14" width="7" style="8" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="6" customWidth="1"/>
-    <col min="16" max="17" width="7.7109375" style="6" customWidth="1"/>
+    <col min="14" max="14" width="7" style="5" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="3" customWidth="1"/>
+    <col min="16" max="17" width="7.7109375" style="3" customWidth="1"/>
     <col min="18" max="18" width="7.7109375" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" style="6" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" style="6" customWidth="1"/>
-    <col min="21" max="21" width="7" style="6" customWidth="1"/>
-    <col min="22" max="22" width="6.28515625" style="6" customWidth="1"/>
+    <col min="19" max="19" width="6.85546875" style="3" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" style="3" customWidth="1"/>
+    <col min="21" max="21" width="7" style="3" customWidth="1"/>
+    <col min="22" max="22" width="6.28515625" style="3" customWidth="1"/>
     <col min="23" max="24" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="N1" s="6"/>
-      <c r="R1" s="6"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="N1" s="3"/>
+      <c r="R1" s="3"/>
     </row>
     <row r="2" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="11" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="N2" s="6"/>
-      <c r="R2" s="6"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="N2" s="3"/>
+      <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19"/>
-      <c r="C3" s="11" t="s">
+      <c r="A3" s="16"/>
+      <c r="C3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="11"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="8"/>
       <c r="I3"/>
       <c r="J3"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="N3" s="6"/>
-      <c r="R3" s="6"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="N3" s="3"/>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
+      <c r="A4" s="16"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
       <c r="K4"/>
-      <c r="L4" s="21"/>
-      <c r="N4" s="6"/>
-      <c r="R4" s="6"/>
+      <c r="L4" s="18"/>
+      <c r="N4" s="3"/>
+      <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="21"/>
-      <c r="N5" s="6"/>
-      <c r="R5" s="6"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="18"/>
+      <c r="N5" s="3"/>
+      <c r="R5" s="3"/>
     </row>
     <row r="6" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="H6" s="6"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="28"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="H6" s="3"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="25"/>
     </row>
     <row r="7" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="32" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="6"/>
-      <c r="R7" s="6"/>
+      <c r="M7" s="3"/>
+      <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1055,22 +1052,22 @@
       </c>
     </row>
     <row r="9" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="6"/>
-      <c r="R9" s="6"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="3"/>
+      <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1078,399 +1075,397 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:20" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="34"/>
-      <c r="B12" s="35" t="s">
+    <row r="12" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="31"/>
+      <c r="B12" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="36" t="s">
+      <c r="G12" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="37" t="s">
+      <c r="I12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="37" t="s">
+      <c r="J12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="46"/>
     </row>
     <row r="13" spans="1:20" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="H13"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
       <c r="K13"/>
       <c r="L13"/>
     </row>
-    <row r="14" spans="1:20" s="46" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="39" t="s">
+    <row r="14" spans="1:20" s="41" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="37"/>
+      <c r="E14" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="F14" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="43" t="s">
+      <c r="G14" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="H14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="D16" s="6"/>
-      <c r="T16" s="47"/>
+      <c r="D16" s="3"/>
+      <c r="T16" s="42"/>
     </row>
     <row r="17" spans="3:20" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="T17" s="47"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="T17" s="42"/>
     </row>
     <row r="18" spans="3:20" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="T18" s="47"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="T18" s="42"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D19" s="6"/>
-      <c r="T19" s="47"/>
+      <c r="D19" s="3"/>
+      <c r="T19" s="42"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D20" s="6"/>
-      <c r="T20" s="47"/>
+      <c r="D20" s="3"/>
+      <c r="T20" s="42"/>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D21" s="6"/>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D22" s="6"/>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D23" s="6"/>
+      <c r="D23" s="3"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D24" s="6"/>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D25" s="6"/>
+      <c r="D25" s="3"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D26" s="6"/>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D27" s="6"/>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D28" s="6"/>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D29" s="6"/>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D30" s="6"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D31" s="6"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D32" s="6"/>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D33" s="6"/>
+      <c r="D33" s="3"/>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D34" s="6"/>
+      <c r="D34" s="3"/>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D35" s="6"/>
+      <c r="D35" s="3"/>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D36" s="6"/>
+      <c r="D36" s="3"/>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D37" s="6"/>
+      <c r="D37" s="3"/>
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D38" s="6"/>
+      <c r="D38" s="3"/>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D39" s="6"/>
+      <c r="D39" s="3"/>
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D40" s="6"/>
+      <c r="D40" s="3"/>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D41" s="6"/>
+      <c r="D41" s="3"/>
     </row>
     <row r="42" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D42" s="6"/>
+      <c r="D42" s="3"/>
     </row>
     <row r="43" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D43" s="6"/>
+      <c r="D43" s="3"/>
     </row>
     <row r="44" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D44" s="6"/>
+      <c r="D44" s="3"/>
     </row>
     <row r="45" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D45" s="6"/>
+      <c r="D45" s="3"/>
     </row>
     <row r="46" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D46" s="6"/>
+      <c r="D46" s="3"/>
     </row>
     <row r="47" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D47" s="6"/>
+      <c r="D47" s="3"/>
     </row>
     <row r="48" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D48" s="6"/>
+      <c r="D48" s="3"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D49" s="6"/>
+      <c r="D49" s="3"/>
     </row>
     <row r="50" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D50" s="6"/>
+      <c r="D50" s="3"/>
     </row>
     <row r="51" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D51" s="6"/>
+      <c r="D51" s="3"/>
     </row>
     <row r="52" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D52" s="6"/>
+      <c r="D52" s="3"/>
     </row>
     <row r="53" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D53" s="6"/>
+      <c r="D53" s="3"/>
     </row>
     <row r="54" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D54" s="6"/>
+      <c r="D54" s="3"/>
     </row>
     <row r="55" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D55" s="6"/>
+      <c r="D55" s="3"/>
     </row>
     <row r="56" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D56" s="6"/>
+      <c r="D56" s="3"/>
     </row>
     <row r="57" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D57" s="6"/>
+      <c r="D57" s="3"/>
     </row>
     <row r="58" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D58" s="6"/>
+      <c r="D58" s="3"/>
     </row>
     <row r="59" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D59" s="6"/>
+      <c r="D59" s="3"/>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D60" s="6"/>
+      <c r="D60" s="3"/>
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D61" s="6"/>
+      <c r="D61" s="3"/>
     </row>
     <row r="62" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D62" s="6"/>
+      <c r="D62" s="3"/>
     </row>
     <row r="63" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D63" s="6"/>
+      <c r="D63" s="3"/>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D64" s="6"/>
+      <c r="D64" s="3"/>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D65" s="6"/>
+      <c r="D65" s="3"/>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D66" s="6"/>
+      <c r="D66" s="3"/>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D67" s="6"/>
+      <c r="D67" s="3"/>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D68" s="6"/>
+      <c r="D68" s="3"/>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D69" s="6"/>
+      <c r="D69" s="3"/>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D70" s="6"/>
+      <c r="D70" s="3"/>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D71" s="6"/>
+      <c r="D71" s="3"/>
     </row>
     <row r="72" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D72" s="6"/>
+      <c r="D72" s="3"/>
     </row>
     <row r="73" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D73" s="6"/>
+      <c r="D73" s="3"/>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D74" s="6"/>
+      <c r="D74" s="3"/>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D75" s="6"/>
+      <c r="D75" s="3"/>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D76" s="6"/>
+      <c r="D76" s="3"/>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D77" s="6"/>
+      <c r="D77" s="3"/>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D78" s="6"/>
+      <c r="D78" s="3"/>
     </row>
     <row r="79" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D79" s="6"/>
+      <c r="D79" s="3"/>
     </row>
     <row r="80" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D80" s="6"/>
+      <c r="D80" s="3"/>
     </row>
     <row r="81" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D81" s="6"/>
+      <c r="D81" s="3"/>
     </row>
     <row r="82" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D82" s="6"/>
+      <c r="D82" s="3"/>
     </row>
     <row r="83" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D83" s="6"/>
+      <c r="D83" s="3"/>
     </row>
     <row r="84" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D84" s="6"/>
+      <c r="D84" s="3"/>
     </row>
     <row r="85" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D85" s="6"/>
+      <c r="D85" s="3"/>
     </row>
     <row r="86" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D86" s="6"/>
+      <c r="D86" s="3"/>
     </row>
     <row r="87" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D87" s="6"/>
+      <c r="D87" s="3"/>
     </row>
     <row r="88" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D88" s="6"/>
+      <c r="D88" s="3"/>
     </row>
     <row r="89" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D89" s="6"/>
+      <c r="D89" s="3"/>
     </row>
     <row r="90" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D90" s="6"/>
+      <c r="D90" s="3"/>
     </row>
     <row r="91" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D91" s="6"/>
+      <c r="D91" s="3"/>
     </row>
     <row r="92" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D92" s="6"/>
+      <c r="D92" s="3"/>
     </row>
     <row r="93" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D93" s="6"/>
+      <c r="D93" s="3"/>
     </row>
     <row r="94" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D94" s="6"/>
+      <c r="D94" s="3"/>
     </row>
     <row r="95" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D95" s="6"/>
+      <c r="D95" s="3"/>
     </row>
     <row r="96" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D96" s="6"/>
+      <c r="D96" s="3"/>
     </row>
     <row r="97" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D97" s="6"/>
+      <c r="D97" s="3"/>
     </row>
     <row r="98" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D98" s="6"/>
+      <c r="D98" s="3"/>
     </row>
     <row r="99" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D99" s="6"/>
+      <c r="D99" s="3"/>
     </row>
     <row r="100" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D100" s="6"/>
+      <c r="D100" s="3"/>
     </row>
     <row r="101" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D101" s="6"/>
+      <c r="D101" s="3"/>
     </row>
     <row r="102" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D102" s="6"/>
+      <c r="D102" s="3"/>
     </row>
     <row r="103" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D103" s="6"/>
+      <c r="D103" s="3"/>
     </row>
     <row r="104" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D104" s="6"/>
+      <c r="D104" s="3"/>
     </row>
     <row r="105" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D105" s="6"/>
+      <c r="D105" s="3"/>
     </row>
     <row r="106" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D106" s="6"/>
+      <c r="D106" s="3"/>
     </row>
     <row r="107" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D107" s="6"/>
+      <c r="D107" s="3"/>
     </row>
     <row r="108" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D108" s="6"/>
+      <c r="D108" s="3"/>
     </row>
     <row r="109" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D109" s="6"/>
+      <c r="D109" s="3"/>
     </row>
     <row r="110" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D110" s="6"/>
+      <c r="D110" s="3"/>
     </row>
     <row r="111" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D111" s="6"/>
+      <c r="D111" s="3"/>
     </row>
     <row r="112" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D112" s="6"/>
+      <c r="D112" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1508,147 +1503,147 @@
     <col min="2" max="2" width="5.7109375" customWidth="1"/>
     <col min="3" max="3" width="41.140625" customWidth="1"/>
     <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="6" customWidth="1"/>
-    <col min="6" max="7" width="14.28515625" style="6" customWidth="1"/>
-    <col min="8" max="10" width="12.140625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="6" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="14.28515625" style="3" customWidth="1"/>
+    <col min="8" max="10" width="12.140625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" style="3" customWidth="1"/>
     <col min="13" max="13" width="7.7109375" customWidth="1"/>
-    <col min="14" max="14" width="7" style="8" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="6" customWidth="1"/>
-    <col min="16" max="17" width="7.7109375" style="6" customWidth="1"/>
+    <col min="14" max="14" width="7" style="5" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="3" customWidth="1"/>
+    <col min="16" max="17" width="7.7109375" style="3" customWidth="1"/>
     <col min="18" max="18" width="7.7109375" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" style="6" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" style="6" customWidth="1"/>
-    <col min="21" max="21" width="7" style="6" customWidth="1"/>
-    <col min="22" max="22" width="6.28515625" style="6" customWidth="1"/>
+    <col min="19" max="19" width="6.85546875" style="3" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" style="3" customWidth="1"/>
+    <col min="21" max="21" width="7" style="3" customWidth="1"/>
+    <col min="22" max="22" width="6.28515625" style="3" customWidth="1"/>
     <col min="23" max="24" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="N1" s="6"/>
-      <c r="R1" s="6"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="N1" s="3"/>
+      <c r="R1" s="3"/>
     </row>
     <row r="2" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="11" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="N2" s="6"/>
-      <c r="R2" s="6"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="N2" s="3"/>
+      <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19"/>
-      <c r="C3" s="11" t="s">
+      <c r="A3" s="16"/>
+      <c r="C3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="11"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="8"/>
       <c r="I3"/>
       <c r="J3"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="N3" s="6"/>
-      <c r="R3" s="6"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="N3" s="3"/>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
+      <c r="A4" s="16"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
       <c r="K4"/>
-      <c r="L4" s="21"/>
-      <c r="N4" s="6"/>
-      <c r="R4" s="6"/>
+      <c r="L4" s="18"/>
+      <c r="N4" s="3"/>
+      <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="21"/>
-      <c r="N5" s="6"/>
-      <c r="R5" s="6"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="18"/>
+      <c r="N5" s="3"/>
+      <c r="R5" s="3"/>
     </row>
     <row r="6" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="H6" s="6"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="28"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="H6" s="3"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="25"/>
     </row>
     <row r="7" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="32" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="6"/>
-      <c r="R7" s="6"/>
+      <c r="M7" s="3"/>
+      <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1656,22 +1651,22 @@
       </c>
     </row>
     <row r="9" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="6"/>
-      <c r="R9" s="6"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="3"/>
+      <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1679,408 +1674,406 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:20" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="34"/>
-      <c r="B12" s="35" t="s">
+    <row r="12" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="31"/>
+      <c r="B12" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="36" t="s">
+      <c r="G12" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="37" t="s">
+      <c r="I12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="37" t="s">
+      <c r="J12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="46"/>
     </row>
     <row r="13" spans="1:20" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="H13"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
       <c r="K13"/>
       <c r="L13"/>
     </row>
-    <row r="14" spans="1:20" s="46" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="39" t="s">
+    <row r="14" spans="1:20" s="41" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="37"/>
+      <c r="E14" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="F14" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="43" t="s">
+      <c r="G14" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="H14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="D16" s="6"/>
-      <c r="T16" s="47"/>
+      <c r="D16" s="3"/>
+      <c r="T16" s="42"/>
     </row>
     <row r="17" spans="3:20" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="T17" s="47"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="T17" s="42"/>
     </row>
     <row r="18" spans="3:20" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="T18" s="47"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="T18" s="42"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D19" s="6"/>
-      <c r="T19" s="47"/>
+      <c r="D19" s="3"/>
+      <c r="T19" s="42"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D20" s="6"/>
-      <c r="T20" s="47"/>
+      <c r="D20" s="3"/>
+      <c r="T20" s="42"/>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D21" s="6"/>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D22" s="6"/>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D23" s="6"/>
+      <c r="D23" s="3"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D24" s="6"/>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D25" s="6"/>
+      <c r="D25" s="3"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D26" s="6"/>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D27" s="6"/>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D28" s="6"/>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D29" s="6"/>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D30" s="6"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D31" s="6"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.2">
-      <c r="D32" s="6"/>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D33" s="6"/>
+      <c r="D33" s="3"/>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D34" s="6"/>
+      <c r="D34" s="3"/>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D35" s="6"/>
+      <c r="D35" s="3"/>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D36" s="6"/>
+      <c r="D36" s="3"/>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D37" s="6"/>
+      <c r="D37" s="3"/>
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D38" s="6"/>
+      <c r="D38" s="3"/>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D39" s="6"/>
+      <c r="D39" s="3"/>
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D40" s="6"/>
+      <c r="D40" s="3"/>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D41" s="6"/>
+      <c r="D41" s="3"/>
     </row>
     <row r="42" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D42" s="6"/>
+      <c r="D42" s="3"/>
     </row>
     <row r="43" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D43" s="6"/>
+      <c r="D43" s="3"/>
     </row>
     <row r="44" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D44" s="6"/>
+      <c r="D44" s="3"/>
     </row>
     <row r="45" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D45" s="6"/>
+      <c r="D45" s="3"/>
     </row>
     <row r="46" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D46" s="6"/>
+      <c r="D46" s="3"/>
     </row>
     <row r="47" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D47" s="6"/>
+      <c r="D47" s="3"/>
     </row>
     <row r="48" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D48" s="6"/>
+      <c r="D48" s="3"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D49" s="6"/>
+      <c r="D49" s="3"/>
     </row>
     <row r="50" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D50" s="6"/>
+      <c r="D50" s="3"/>
     </row>
     <row r="51" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D51" s="6"/>
+      <c r="D51" s="3"/>
     </row>
     <row r="52" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D52" s="6"/>
+      <c r="D52" s="3"/>
     </row>
     <row r="53" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D53" s="6"/>
+      <c r="D53" s="3"/>
     </row>
     <row r="54" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D54" s="6"/>
+      <c r="D54" s="3"/>
     </row>
     <row r="55" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D55" s="6"/>
+      <c r="D55" s="3"/>
     </row>
     <row r="56" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D56" s="6"/>
+      <c r="D56" s="3"/>
     </row>
     <row r="57" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D57" s="6"/>
+      <c r="D57" s="3"/>
     </row>
     <row r="58" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D58" s="6"/>
+      <c r="D58" s="3"/>
     </row>
     <row r="59" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D59" s="6"/>
+      <c r="D59" s="3"/>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D60" s="6"/>
+      <c r="D60" s="3"/>
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D61" s="6"/>
+      <c r="D61" s="3"/>
     </row>
     <row r="62" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D62" s="6"/>
+      <c r="D62" s="3"/>
     </row>
     <row r="63" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D63" s="6"/>
+      <c r="D63" s="3"/>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D64" s="6"/>
+      <c r="D64" s="3"/>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D65" s="6"/>
+      <c r="D65" s="3"/>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D66" s="6"/>
+      <c r="D66" s="3"/>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D67" s="6"/>
+      <c r="D67" s="3"/>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D68" s="6"/>
+      <c r="D68" s="3"/>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D69" s="6"/>
+      <c r="D69" s="3"/>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D70" s="6"/>
+      <c r="D70" s="3"/>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D71" s="6"/>
+      <c r="D71" s="3"/>
     </row>
     <row r="72" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D72" s="6"/>
+      <c r="D72" s="3"/>
     </row>
     <row r="73" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D73" s="6"/>
+      <c r="D73" s="3"/>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D74" s="6"/>
+      <c r="D74" s="3"/>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D75" s="6"/>
+      <c r="D75" s="3"/>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D76" s="6"/>
+      <c r="D76" s="3"/>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D77" s="6"/>
+      <c r="D77" s="3"/>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D78" s="6"/>
+      <c r="D78" s="3"/>
     </row>
     <row r="79" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D79" s="6"/>
+      <c r="D79" s="3"/>
     </row>
     <row r="80" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D80" s="6"/>
+      <c r="D80" s="3"/>
     </row>
     <row r="81" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D81" s="6"/>
+      <c r="D81" s="3"/>
     </row>
     <row r="82" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D82" s="6"/>
+      <c r="D82" s="3"/>
     </row>
     <row r="83" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D83" s="6"/>
+      <c r="D83" s="3"/>
     </row>
     <row r="84" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D84" s="6"/>
+      <c r="D84" s="3"/>
     </row>
     <row r="85" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D85" s="6"/>
+      <c r="D85" s="3"/>
     </row>
     <row r="86" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D86" s="6"/>
+      <c r="D86" s="3"/>
     </row>
     <row r="87" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D87" s="6"/>
+      <c r="D87" s="3"/>
     </row>
     <row r="88" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D88" s="6"/>
+      <c r="D88" s="3"/>
     </row>
     <row r="89" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D89" s="6"/>
+      <c r="D89" s="3"/>
     </row>
     <row r="90" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D90" s="6"/>
+      <c r="D90" s="3"/>
     </row>
     <row r="91" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D91" s="6"/>
+      <c r="D91" s="3"/>
     </row>
     <row r="92" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D92" s="6"/>
+      <c r="D92" s="3"/>
     </row>
     <row r="93" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D93" s="6"/>
+      <c r="D93" s="3"/>
     </row>
     <row r="94" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D94" s="6"/>
+      <c r="D94" s="3"/>
     </row>
     <row r="95" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D95" s="6"/>
+      <c r="D95" s="3"/>
     </row>
     <row r="96" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D96" s="6"/>
+      <c r="D96" s="3"/>
     </row>
     <row r="97" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D97" s="6"/>
+      <c r="D97" s="3"/>
     </row>
     <row r="98" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D98" s="6"/>
+      <c r="D98" s="3"/>
     </row>
     <row r="99" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D99" s="6"/>
+      <c r="D99" s="3"/>
     </row>
     <row r="100" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D100" s="6"/>
+      <c r="D100" s="3"/>
     </row>
     <row r="101" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D101" s="6"/>
+      <c r="D101" s="3"/>
     </row>
     <row r="102" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D102" s="6"/>
+      <c r="D102" s="3"/>
     </row>
     <row r="103" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D103" s="6"/>
+      <c r="D103" s="3"/>
     </row>
     <row r="104" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D104" s="6"/>
+      <c r="D104" s="3"/>
     </row>
     <row r="105" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D105" s="6"/>
+      <c r="D105" s="3"/>
     </row>
     <row r="106" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D106" s="6"/>
+      <c r="D106" s="3"/>
     </row>
     <row r="107" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D107" s="6"/>
+      <c r="D107" s="3"/>
     </row>
     <row r="108" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D108" s="6"/>
+      <c r="D108" s="3"/>
     </row>
     <row r="109" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D109" s="6"/>
+      <c r="D109" s="3"/>
     </row>
     <row r="110" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D110" s="6"/>
+      <c r="D110" s="3"/>
     </row>
     <row r="111" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D111" s="6"/>
+      <c r="D111" s="3"/>
     </row>
     <row r="112" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D112" s="6"/>
+      <c r="D112" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="D18:H18"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="K12:L12"/>
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation showErrorMessage="1" sqref="L6" xr:uid="{DA08E795-521B-4C74-BA00-7D936560033E}">

--- a/owlcms/src/main/resources/templates/weighin/_WeighInForm_x2-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/weighin/_WeighInForm_x2-LETTER.xlsx
@@ -1,104 +1,73 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\weighin\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A07800-3CB9-471A-B1A4-D9C46EF5D402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="28680" yWindow="1815" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Weigh-in" sheetId="1" r:id="rId1"/>
-    <sheet name="Weigh-in (2)" sheetId="2" r:id="rId2"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_1Excel_BuiltIn_Criteria_1_1" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="_1Excel_BuiltIn_Criteria_1_1">'Weigh-in'!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Weigh-in'!$A$14:$L$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weigh-in (2)'!$A$14:$L$14</definedName>
-    <definedName name="AFF." localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="AFF.">'Weigh-in'!#REF!</definedName>
-    <definedName name="Affiliation" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="Affiliation">'Weigh-in'!#REF!</definedName>
-    <definedName name="Barre">#REF!</definedName>
-    <definedName name="calcA" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="calcA">'Weigh-in'!#REF!</definedName>
-    <definedName name="CAT." localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="CAT.">'Weigh-in'!#REF!</definedName>
-    <definedName name="CategoryFilter" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="CategoryFilter">'Weigh-in'!#REF!</definedName>
-    <definedName name="CLUB" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="CLUB">'Weigh-in'!#REF!</definedName>
-    <definedName name="Collet">#REF!</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="0">'Weigh-in'!$A$1:$CO$86</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="1">'Weigh-in (2)'!$A$1:$CO$86</definedName>
-    <definedName name="demandé" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="demandé">'Weigh-in'!#REF!</definedName>
-    <definedName name="dernier" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="dernier">'Weigh-in'!#REF!</definedName>
-    <definedName name="essais" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="essais">'Weigh-in'!#REF!</definedName>
-    <definedName name="essaisArr" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="essaisArr">'Weigh-in'!#REF!</definedName>
-    <definedName name="GroupeCourant" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="GroupeCourant">'Weigh-in'!#REF!</definedName>
-    <definedName name="Groupes">#REF!</definedName>
-    <definedName name="GroupFilter" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="GroupFilter">'Weigh-in'!#REF!</definedName>
-    <definedName name="InactiveGroupFilter" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="InactiveGroupFilter">'Weigh-in'!#REF!</definedName>
-    <definedName name="isSnatch" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="isSnatch">'Weigh-in'!#REF!</definedName>
-    <definedName name="lbParKg" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="lbParKg">'Weigh-in'!#REF!</definedName>
-    <definedName name="LignesCalculs" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="LignesCalculs">'Weigh-in'!#REF!</definedName>
-    <definedName name="LignesEntête" localSheetId="1">'Weigh-in (2)'!$1:$9</definedName>
-    <definedName name="LignesEntête">'Weigh-in'!$1:$9</definedName>
-    <definedName name="LignesOfficiels" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="LignesOfficiels">'Weigh-in'!#REF!</definedName>
-    <definedName name="M_F" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="M_F">'Weigh-in'!#REF!</definedName>
-    <definedName name="NAIS." localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="NAIS.">'Weigh-in'!#REF!</definedName>
-    <definedName name="NbCollet">#REF!</definedName>
-    <definedName name="NOM" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="NOM">'Weigh-in'!#REF!</definedName>
-    <definedName name="nombreLevers" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="nombreLevers">'Weigh-in'!#REF!</definedName>
-    <definedName name="P.C." localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="P.C.">'Weigh-in'!#REF!</definedName>
-    <definedName name="PeséeGroupFilter" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="PeséeGroupFilter">'Weigh-in'!#REF!</definedName>
-    <definedName name="PRÉNOM" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="PRÉNOM">'Weigh-in'!#REF!</definedName>
-    <definedName name="progr." localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="progr.">'Weigh-in'!#REF!</definedName>
-    <definedName name="requestedCJ" localSheetId="1">'Weigh-in (2)'!$R:$R</definedName>
-    <definedName name="requestedCJ">'Weigh-in'!$R:$R</definedName>
-    <definedName name="StartGroupFilter" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="StartGroupFilter">'Weigh-in'!#REF!</definedName>
-    <definedName name="TAS" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="TAS">'Weigh-in'!#REF!</definedName>
-    <definedName name="tirage" localSheetId="1">'Weigh-in (2)'!#REF!</definedName>
-    <definedName name="tirage">'Weigh-in'!#REF!</definedName>
-  </definedNames>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
-</workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns8="http://schemas.libreoffice.org/" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15 xr xr6 xr10 xr2">
+  <ns0:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <ns0:workbookPr/>
+  <ns1:AlternateContent>
+    <ns1:Choice Requires="x15">
+      <ns2:absPath url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\weighin\"/>
+    </ns1:Choice>
+  </ns1:AlternateContent>
+  <ns3:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E225AA8-7634-4552-9B56-1A1292ECD058}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <ns0:bookViews>
+    <ns0:workbookView xWindow="28680" yWindow="1815" windowWidth="29040" windowHeight="15720" tabRatio="500" ns6:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </ns0:bookViews>
+  <ns0:sheets>
+    <ns0:sheet name="Weigh-in" sheetId="1" r:id="rId1"/>
+    <ns0:sheet name="Weigh-in (2)" sheetId="2" r:id="rId5"/>
+  </ns0:sheets>
+  <ns0:definedNames>
+    <ns0:definedName name="_1Excel_BuiltIn_Criteria_1_1">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Weigh-in'!$A$14:$L$14</ns0:definedName>
+    <ns0:definedName name="AFF.">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="Affiliation">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="Barre">#REF!</ns0:definedName>
+    <ns0:definedName name="calcA">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="CAT.">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="CategoryFilter">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="CLUB">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="Collet">#REF!</ns0:definedName>
+    <ns0:definedName name="_xlnm.Criteria" localSheetId="0">'Weigh-in'!$A$1:$CO$86</ns0:definedName>
+    <ns0:definedName name="demandé">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="dernier">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="essais">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="essaisArr">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="GroupeCourant">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="Groupes">#REF!</ns0:definedName>
+    <ns0:definedName name="GroupFilter">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="InactiveGroupFilter">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="isSnatch">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="lbParKg">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="LignesCalculs">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="LignesEntête">'Weigh-in'!$1:$9</ns0:definedName>
+    <ns0:definedName name="LignesOfficiels">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="M_F">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="NAIS.">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="NbCollet">#REF!</ns0:definedName>
+    <ns0:definedName name="NOM">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="nombreLevers">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="P.C.">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="PeséeGroupFilter">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="PRÉNOM">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="progr.">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="requestedCJ">'Weigh-in'!$R:$R</ns0:definedName>
+    <ns0:definedName name="StartGroupFilter">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="TAS">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="tirage">'Weigh-in'!#REF!</ns0:definedName>
+    <ns0:definedName name="_xlnm.Print_Area" localSheetId="0">'Weigh-in'!$A:$L</ns0:definedName>
+    <ns0:definedName name="_xlnm.Print_Area" localSheetId="1">'Weigh-in (2)'!$A:$L</ns0:definedName>
+  </ns0:definedNames>
+  <ns0:calcPr calcId="0"/>
+  <ns0:extLst>
+    <ns0:ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <ns8:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ns0:ext>
+  </ns0:extLst>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>${t.get("Competition.competitionName")} :</t>
   </si>
@@ -208,12 +177,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="20" ns2:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -470,7 +439,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -619,20 +588,24 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
-    <cellStyle name="Emphase 1" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Emphase 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Emphase 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Emphase 1" xfId="2" ns3:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Emphase 2" xfId="3" ns3:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Emphase 3" xfId="4" ns3:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Lien hypertexte 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Lien hypertexte 2" xfId="5" ns3:uid="{00000000-0005-0000-0000-000009000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="6" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Normal 3" xfId="7" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Titre 1" xfId="8" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Titre 1 1" xfId="9" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Titre 1 1 1" xfId="10" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Titre de la feuille" xfId="11" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Normal 2" xfId="6" ns3:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 3" xfId="7" ns3:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Titre 1" xfId="8" ns3:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Titre 1 1" xfId="9" ns3:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Titre 1 1 1" xfId="10" ns3:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Titre de la feuille" xfId="11" ns3:uid="{00000000-0005-0000-0000-00000F000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -705,11 +678,11 @@
     </indexedColors>
   </colors>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns4:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns5:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -893,12 +866,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V112"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.75" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.7109375" customWidth="1"/>
@@ -921,7 +894,7 @@
     <col min="23" max="24" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="7"/>
       <c r="C1" s="8" t="s">
@@ -941,7 +914,7 @@
       <c r="N1" s="3"/>
       <c r="R1" s="3"/>
     </row>
-    <row r="2" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="10"/>
       <c r="C2" s="8" t="s">
@@ -961,7 +934,7 @@
       <c r="N2" s="3"/>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="C3" s="8" t="s">
         <v>4</v>
@@ -980,7 +953,7 @@
       <c r="N3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="C4" s="8"/>
       <c r="D4" s="19"/>
@@ -995,7 +968,7 @@
       <c r="N4" s="3"/>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.3">
       <c r="A5" s="16"/>
       <c r="B5" s="45" t="s">
         <v>6</v>
@@ -1013,7 +986,7 @@
       <c r="N5" s="3"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A6" s="21"/>
       <c r="B6" s="22"/>
       <c r="C6" s="23"/>
@@ -1026,7 +999,7 @@
       <c r="Q6" s="8"/>
       <c r="R6" s="25"/>
     </row>
-    <row r="7" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A7" s="26" t="s">
         <v>7</v>
       </c>
@@ -1046,12 +1019,12 @@
       <c r="M7" s="3"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ht="13.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ht="25.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A9" s="26" t="s">
         <v>10</v>
       </c>
@@ -1069,13 +1042,13 @@
       <c r="M9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="12.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ht="6" customHeight="1" ns3:dyDescent="0.2"/>
+    <row r="12" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.2">
       <c r="A12" s="31"/>
       <c r="B12" s="32" t="s">
         <v>12</v>
@@ -1109,7 +1082,7 @@
       </c>
       <c r="L12" s="46"/>
     </row>
-    <row r="13" spans="1:20" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="14.25" ns3:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1119,14 +1092,14 @@
       <c r="K13"/>
       <c r="L13"/>
     </row>
-    <row r="14" spans="1:20" s="41" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" s="41" customFormat="1" ht="32.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A14" s="35" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="48" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="37"/>
@@ -1147,17 +1120,17 @@
       <c r="K14" s="47"/>
       <c r="L14" s="47"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ns3:dyDescent="0.2">
       <c r="A15" t="s">
         <v>30</v>
       </c>
       <c r="E15"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" ns3:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="T16" s="42"/>
     </row>
-    <row r="17" spans="3:20" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:20" ht="33" customHeight="1" ns3:dyDescent="0.2">
       <c r="C17" t="s">
         <v>31</v>
       </c>
@@ -1170,7 +1143,7 @@
       <c r="H17" s="43"/>
       <c r="T17" s="42"/>
     </row>
-    <row r="18" spans="3:20" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" ht="33" customHeight="1" ns3:dyDescent="0.2">
       <c r="C18" t="s">
         <v>33</v>
       </c>
@@ -1183,288 +1156,288 @@
       <c r="H18" s="43"/>
       <c r="T18" s="42"/>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" ns3:dyDescent="0.2">
       <c r="D19" s="3"/>
       <c r="T19" s="42"/>
     </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:20" ns3:dyDescent="0.2">
       <c r="D20" s="3"/>
       <c r="T20" s="42"/>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" ns3:dyDescent="0.2">
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" ns3:dyDescent="0.2">
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" ns3:dyDescent="0.2">
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" ns3:dyDescent="0.2">
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" ns3:dyDescent="0.2">
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:20" ns3:dyDescent="0.2">
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" ns3:dyDescent="0.2">
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" ns3:dyDescent="0.2">
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:20" ns3:dyDescent="0.2">
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:20" ns3:dyDescent="0.2">
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:20" ns3:dyDescent="0.2">
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:20" ns3:dyDescent="0.2">
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="4:4" ns3:dyDescent="0.2">
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="4:4" ns3:dyDescent="0.2">
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="4:4" ns3:dyDescent="0.2">
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="4:4" ns3:dyDescent="0.2">
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="4:4" ns3:dyDescent="0.2">
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="4:4" ns3:dyDescent="0.2">
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="4:4" ns3:dyDescent="0.2">
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="4:4" ns3:dyDescent="0.2">
       <c r="D40" s="3"/>
     </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="4:4" ns3:dyDescent="0.2">
       <c r="D41" s="3"/>
     </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="4:4" ns3:dyDescent="0.2">
       <c r="D42" s="3"/>
     </row>
-    <row r="43" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="4:4" ns3:dyDescent="0.2">
       <c r="D43" s="3"/>
     </row>
-    <row r="44" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="4:4" ns3:dyDescent="0.2">
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="4:4" ns3:dyDescent="0.2">
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="4:4" ns3:dyDescent="0.2">
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="4:4" ns3:dyDescent="0.2">
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="4:4" ns3:dyDescent="0.2">
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="4:4" ns3:dyDescent="0.2">
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="4:4" ns3:dyDescent="0.2">
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="4:4" ns3:dyDescent="0.2">
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="4:4" ns3:dyDescent="0.2">
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="4:4" ns3:dyDescent="0.2">
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="4:4" ns3:dyDescent="0.2">
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="4:4" ns3:dyDescent="0.2">
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="4:4" ns3:dyDescent="0.2">
       <c r="D56" s="3"/>
     </row>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="4:4" ns3:dyDescent="0.2">
       <c r="D57" s="3"/>
     </row>
-    <row r="58" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="4:4" ns3:dyDescent="0.2">
       <c r="D58" s="3"/>
     </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="4:4" ns3:dyDescent="0.2">
       <c r="D59" s="3"/>
     </row>
-    <row r="60" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="4:4" ns3:dyDescent="0.2">
       <c r="D60" s="3"/>
     </row>
-    <row r="61" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="4:4" ns3:dyDescent="0.2">
       <c r="D61" s="3"/>
     </row>
-    <row r="62" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="4:4" ns3:dyDescent="0.2">
       <c r="D62" s="3"/>
     </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="4:4" ns3:dyDescent="0.2">
       <c r="D63" s="3"/>
     </row>
-    <row r="64" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="4:4" ns3:dyDescent="0.2">
       <c r="D64" s="3"/>
     </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="4:4" ns3:dyDescent="0.2">
       <c r="D65" s="3"/>
     </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="4:4" ns3:dyDescent="0.2">
       <c r="D66" s="3"/>
     </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="4:4" ns3:dyDescent="0.2">
       <c r="D67" s="3"/>
     </row>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="4:4" ns3:dyDescent="0.2">
       <c r="D68" s="3"/>
     </row>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="4:4" ns3:dyDescent="0.2">
       <c r="D69" s="3"/>
     </row>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="4:4" ns3:dyDescent="0.2">
       <c r="D70" s="3"/>
     </row>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="4:4" ns3:dyDescent="0.2">
       <c r="D71" s="3"/>
     </row>
-    <row r="72" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="4:4" ns3:dyDescent="0.2">
       <c r="D72" s="3"/>
     </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="4:4" ns3:dyDescent="0.2">
       <c r="D73" s="3"/>
     </row>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="4:4" ns3:dyDescent="0.2">
       <c r="D74" s="3"/>
     </row>
-    <row r="75" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="4:4" ns3:dyDescent="0.2">
       <c r="D75" s="3"/>
     </row>
-    <row r="76" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="4:4" ns3:dyDescent="0.2">
       <c r="D76" s="3"/>
     </row>
-    <row r="77" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="4:4" ns3:dyDescent="0.2">
       <c r="D77" s="3"/>
     </row>
-    <row r="78" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="4:4" ns3:dyDescent="0.2">
       <c r="D78" s="3"/>
     </row>
-    <row r="79" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="4:4" ns3:dyDescent="0.2">
       <c r="D79" s="3"/>
     </row>
-    <row r="80" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="4:4" ns3:dyDescent="0.2">
       <c r="D80" s="3"/>
     </row>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="4:4" ns3:dyDescent="0.2">
       <c r="D81" s="3"/>
     </row>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="4:4" ns3:dyDescent="0.2">
       <c r="D82" s="3"/>
     </row>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="4:4" ns3:dyDescent="0.2">
       <c r="D83" s="3"/>
     </row>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="4:4" ns3:dyDescent="0.2">
       <c r="D84" s="3"/>
     </row>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="4:4" ns3:dyDescent="0.2">
       <c r="D85" s="3"/>
     </row>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="4:4" ns3:dyDescent="0.2">
       <c r="D86" s="3"/>
     </row>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="4:4" ns3:dyDescent="0.2">
       <c r="D87" s="3"/>
     </row>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="4:4" ns3:dyDescent="0.2">
       <c r="D88" s="3"/>
     </row>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="4:4" ns3:dyDescent="0.2">
       <c r="D89" s="3"/>
     </row>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="4:4" ns3:dyDescent="0.2">
       <c r="D90" s="3"/>
     </row>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="4:4" ns3:dyDescent="0.2">
       <c r="D91" s="3"/>
     </row>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="4:4" ns3:dyDescent="0.2">
       <c r="D92" s="3"/>
     </row>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="4:4" ns3:dyDescent="0.2">
       <c r="D93" s="3"/>
     </row>
-    <row r="94" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="4:4" ns3:dyDescent="0.2">
       <c r="D94" s="3"/>
     </row>
-    <row r="95" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="4:4" ns3:dyDescent="0.2">
       <c r="D95" s="3"/>
     </row>
-    <row r="96" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="4:4" ns3:dyDescent="0.2">
       <c r="D96" s="3"/>
     </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="4:4" ns3:dyDescent="0.2">
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="4:4" ns3:dyDescent="0.2">
       <c r="D98" s="3"/>
     </row>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="4:4" ns3:dyDescent="0.2">
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="4:4" ns3:dyDescent="0.2">
       <c r="D100" s="3"/>
     </row>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="4:4" ns3:dyDescent="0.2">
       <c r="D101" s="3"/>
     </row>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="4:4" ns3:dyDescent="0.2">
       <c r="D102" s="3"/>
     </row>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="4:4" ns3:dyDescent="0.2">
       <c r="D103" s="3"/>
     </row>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="4:4" ns3:dyDescent="0.2">
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="4:4" ns3:dyDescent="0.2">
       <c r="D105" s="3"/>
     </row>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="4:4" ns3:dyDescent="0.2">
       <c r="D106" s="3"/>
     </row>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="4:4" ns3:dyDescent="0.2">
       <c r="D107" s="3"/>
     </row>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="4:4" ns3:dyDescent="0.2">
       <c r="D108" s="3"/>
     </row>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="4:4" ns3:dyDescent="0.2">
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="4:4" ns3:dyDescent="0.2">
       <c r="D110" s="3"/>
     </row>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="4:4" ns3:dyDescent="0.2">
       <c r="D111" s="3"/>
     </row>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="4:4" ns3:dyDescent="0.2">
       <c r="D112" s="3"/>
     </row>
   </sheetData>
@@ -1476,28 +1449,18 @@
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="D17:H17"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="D14 F15:G15" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>0</formula1>
-      <formula2>200</formula2>
-    </dataValidation>
-    <dataValidation showErrorMessage="1" sqref="L6" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.31527777777777799" right="0.35416666666666702" top="0.39374999999999999" bottom="0.39374999999999999" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AEABB75-7895-4A7F-B970-E3DC71059BA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V112"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.75" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.7109375" customWidth="1"/>
@@ -1520,7 +1483,7 @@
     <col min="23" max="24" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="7"/>
       <c r="C1" s="8" t="s">
@@ -1540,7 +1503,7 @@
       <c r="N1" s="3"/>
       <c r="R1" s="3"/>
     </row>
-    <row r="2" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="10"/>
       <c r="C2" s="8" t="s">
@@ -1560,7 +1523,7 @@
       <c r="N2" s="3"/>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="C3" s="8" t="s">
         <v>4</v>
@@ -1579,7 +1542,7 @@
       <c r="N3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="C4" s="8"/>
       <c r="D4" s="19"/>
@@ -1594,7 +1557,7 @@
       <c r="N4" s="3"/>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.3">
       <c r="A5" s="16"/>
       <c r="B5" s="45" t="s">
         <v>6</v>
@@ -1612,7 +1575,7 @@
       <c r="N5" s="3"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A6" s="21"/>
       <c r="B6" s="22"/>
       <c r="C6" s="23"/>
@@ -1625,7 +1588,7 @@
       <c r="Q6" s="8"/>
       <c r="R6" s="25"/>
     </row>
-    <row r="7" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A7" s="26" t="s">
         <v>7</v>
       </c>
@@ -1645,12 +1608,12 @@
       <c r="M7" s="3"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" ht="13.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" ht="25.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A9" s="26" t="s">
         <v>10</v>
       </c>
@@ -1668,13 +1631,13 @@
       <c r="M9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="12.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ht="6" customHeight="1" ns3:dyDescent="0.2"/>
+    <row r="12" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.2">
       <c r="A12" s="31"/>
       <c r="B12" s="32" t="s">
         <v>12</v>
@@ -1708,7 +1671,7 @@
       </c>
       <c r="L12" s="46"/>
     </row>
-    <row r="13" spans="1:20" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="14.25" ns3:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1718,14 +1681,14 @@
       <c r="K13"/>
       <c r="L13"/>
     </row>
-    <row r="14" spans="1:20" s="41" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" s="41" customFormat="1" ht="32.25" customHeight="1" ns3:dyDescent="0.2">
       <c r="A14" s="35" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="48" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="37"/>
@@ -1746,17 +1709,17 @@
       <c r="K14" s="47"/>
       <c r="L14" s="47"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ns3:dyDescent="0.2">
       <c r="A15" t="s">
         <v>30</v>
       </c>
       <c r="E15"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" ns3:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="T16" s="42"/>
     </row>
-    <row r="17" spans="3:20" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:20" ht="33" customHeight="1" ns3:dyDescent="0.2">
       <c r="C17" t="s">
         <v>31</v>
       </c>
@@ -1769,7 +1732,7 @@
       <c r="H17" s="43"/>
       <c r="T17" s="42"/>
     </row>
-    <row r="18" spans="3:20" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" ht="33" customHeight="1" ns3:dyDescent="0.2">
       <c r="C18" t="s">
         <v>33</v>
       </c>
@@ -1782,288 +1745,288 @@
       <c r="H18" s="43"/>
       <c r="T18" s="42"/>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" ns3:dyDescent="0.2">
       <c r="D19" s="3"/>
       <c r="T19" s="42"/>
     </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:20" ns3:dyDescent="0.2">
       <c r="D20" s="3"/>
       <c r="T20" s="42"/>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" ns3:dyDescent="0.2">
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" ns3:dyDescent="0.2">
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" ns3:dyDescent="0.2">
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" ns3:dyDescent="0.2">
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" ns3:dyDescent="0.2">
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:20" ns3:dyDescent="0.2">
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" ns3:dyDescent="0.2">
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" ns3:dyDescent="0.2">
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:20" ns3:dyDescent="0.2">
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:20" ns3:dyDescent="0.2">
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:20" ns3:dyDescent="0.2">
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:20" ns3:dyDescent="0.2">
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="4:4" ns3:dyDescent="0.2">
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="4:4" ns3:dyDescent="0.2">
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="4:4" ns3:dyDescent="0.2">
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="4:4" ns3:dyDescent="0.2">
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="4:4" ns3:dyDescent="0.2">
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="4:4" ns3:dyDescent="0.2">
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="4:4" ns3:dyDescent="0.2">
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="4:4" ns3:dyDescent="0.2">
       <c r="D40" s="3"/>
     </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="4:4" ns3:dyDescent="0.2">
       <c r="D41" s="3"/>
     </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="4:4" ns3:dyDescent="0.2">
       <c r="D42" s="3"/>
     </row>
-    <row r="43" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="4:4" ns3:dyDescent="0.2">
       <c r="D43" s="3"/>
     </row>
-    <row r="44" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="4:4" ns3:dyDescent="0.2">
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="4:4" ns3:dyDescent="0.2">
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="4:4" ns3:dyDescent="0.2">
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="4:4" ns3:dyDescent="0.2">
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="4:4" ns3:dyDescent="0.2">
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="4:4" ns3:dyDescent="0.2">
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="4:4" ns3:dyDescent="0.2">
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="4:4" ns3:dyDescent="0.2">
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="4:4" ns3:dyDescent="0.2">
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="4:4" ns3:dyDescent="0.2">
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="4:4" ns3:dyDescent="0.2">
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="4:4" ns3:dyDescent="0.2">
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="4:4" ns3:dyDescent="0.2">
       <c r="D56" s="3"/>
     </row>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="4:4" ns3:dyDescent="0.2">
       <c r="D57" s="3"/>
     </row>
-    <row r="58" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="4:4" ns3:dyDescent="0.2">
       <c r="D58" s="3"/>
     </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="4:4" ns3:dyDescent="0.2">
       <c r="D59" s="3"/>
     </row>
-    <row r="60" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="4:4" ns3:dyDescent="0.2">
       <c r="D60" s="3"/>
     </row>
-    <row r="61" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="4:4" ns3:dyDescent="0.2">
       <c r="D61" s="3"/>
     </row>
-    <row r="62" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="4:4" ns3:dyDescent="0.2">
       <c r="D62" s="3"/>
     </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="4:4" ns3:dyDescent="0.2">
       <c r="D63" s="3"/>
     </row>
-    <row r="64" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="4:4" ns3:dyDescent="0.2">
       <c r="D64" s="3"/>
     </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="4:4" ns3:dyDescent="0.2">
       <c r="D65" s="3"/>
     </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="4:4" ns3:dyDescent="0.2">
       <c r="D66" s="3"/>
     </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="4:4" ns3:dyDescent="0.2">
       <c r="D67" s="3"/>
     </row>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="4:4" ns3:dyDescent="0.2">
       <c r="D68" s="3"/>
     </row>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="4:4" ns3:dyDescent="0.2">
       <c r="D69" s="3"/>
     </row>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="4:4" ns3:dyDescent="0.2">
       <c r="D70" s="3"/>
     </row>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="4:4" ns3:dyDescent="0.2">
       <c r="D71" s="3"/>
     </row>
-    <row r="72" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="4:4" ns3:dyDescent="0.2">
       <c r="D72" s="3"/>
     </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="4:4" ns3:dyDescent="0.2">
       <c r="D73" s="3"/>
     </row>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="4:4" ns3:dyDescent="0.2">
       <c r="D74" s="3"/>
     </row>
-    <row r="75" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="4:4" ns3:dyDescent="0.2">
       <c r="D75" s="3"/>
     </row>
-    <row r="76" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="4:4" ns3:dyDescent="0.2">
       <c r="D76" s="3"/>
     </row>
-    <row r="77" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="4:4" ns3:dyDescent="0.2">
       <c r="D77" s="3"/>
     </row>
-    <row r="78" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="4:4" ns3:dyDescent="0.2">
       <c r="D78" s="3"/>
     </row>
-    <row r="79" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="4:4" ns3:dyDescent="0.2">
       <c r="D79" s="3"/>
     </row>
-    <row r="80" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="4:4" ns3:dyDescent="0.2">
       <c r="D80" s="3"/>
     </row>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="4:4" ns3:dyDescent="0.2">
       <c r="D81" s="3"/>
     </row>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="4:4" ns3:dyDescent="0.2">
       <c r="D82" s="3"/>
     </row>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="4:4" ns3:dyDescent="0.2">
       <c r="D83" s="3"/>
     </row>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="4:4" ns3:dyDescent="0.2">
       <c r="D84" s="3"/>
     </row>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="4:4" ns3:dyDescent="0.2">
       <c r="D85" s="3"/>
     </row>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="4:4" ns3:dyDescent="0.2">
       <c r="D86" s="3"/>
     </row>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="4:4" ns3:dyDescent="0.2">
       <c r="D87" s="3"/>
     </row>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="4:4" ns3:dyDescent="0.2">
       <c r="D88" s="3"/>
     </row>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="4:4" ns3:dyDescent="0.2">
       <c r="D89" s="3"/>
     </row>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="4:4" ns3:dyDescent="0.2">
       <c r="D90" s="3"/>
     </row>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="4:4" ns3:dyDescent="0.2">
       <c r="D91" s="3"/>
     </row>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="4:4" ns3:dyDescent="0.2">
       <c r="D92" s="3"/>
     </row>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="4:4" ns3:dyDescent="0.2">
       <c r="D93" s="3"/>
     </row>
-    <row r="94" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="4:4" ns3:dyDescent="0.2">
       <c r="D94" s="3"/>
     </row>
-    <row r="95" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="4:4" ns3:dyDescent="0.2">
       <c r="D95" s="3"/>
     </row>
-    <row r="96" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="4:4" ns3:dyDescent="0.2">
       <c r="D96" s="3"/>
     </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="4:4" ns3:dyDescent="0.2">
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="4:4" ns3:dyDescent="0.2">
       <c r="D98" s="3"/>
     </row>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="4:4" ns3:dyDescent="0.2">
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="4:4" ns3:dyDescent="0.2">
       <c r="D100" s="3"/>
     </row>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="4:4" ns3:dyDescent="0.2">
       <c r="D101" s="3"/>
     </row>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="4:4" ns3:dyDescent="0.2">
       <c r="D102" s="3"/>
     </row>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="4:4" ns3:dyDescent="0.2">
       <c r="D103" s="3"/>
     </row>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="4:4" ns3:dyDescent="0.2">
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="4:4" ns3:dyDescent="0.2">
       <c r="D105" s="3"/>
     </row>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="4:4" ns3:dyDescent="0.2">
       <c r="D106" s="3"/>
     </row>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="4:4" ns3:dyDescent="0.2">
       <c r="D107" s="3"/>
     </row>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="4:4" ns3:dyDescent="0.2">
       <c r="D108" s="3"/>
     </row>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="4:4" ns3:dyDescent="0.2">
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="4:4" ns3:dyDescent="0.2">
       <c r="D110" s="3"/>
     </row>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="4:4" ns3:dyDescent="0.2">
       <c r="D111" s="3"/>
     </row>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="4:4" ns3:dyDescent="0.2">
       <c r="D112" s="3"/>
     </row>
   </sheetData>
@@ -2075,16 +2038,6 @@
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="D17:H17"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation showErrorMessage="1" sqref="L6" xr:uid="{DA08E795-521B-4C74-BA00-7D936560033E}">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="D14 F15:G15" xr:uid="{5A93E1A8-AF40-40E3-9C28-F074ED597242}">
-      <formula1>0</formula1>
-      <formula2>200</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.31527777777777799" right="0.35416666666666702" top="0.39374999999999999" bottom="0.39374999999999999" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/owlcms/src/main/resources/templates/weighin/_WeighInForm_x2-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/weighin/_WeighInForm_x2-LETTER.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns8="http://schemas.libreoffice.org/" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15 xr xr6 xr10 xr2">
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns8="http://schemas.libreoffice.org/" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <ns0:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <ns0:workbookPr/>
-  <ns1:AlternateContent>
-    <ns1:Choice Requires="x15">
-      <ns2:absPath url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\weighin\"/>
-    </ns1:Choice>
-  </ns1:AlternateContent>
-  <ns3:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E225AA8-7634-4552-9B56-1A1292ECD058}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <ns0:bookViews>
-    <ns0:workbookView xWindow="28680" yWindow="1815" windowWidth="29040" windowHeight="15720" tabRatio="500" ns6:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <ns0:workbookView xWindow="28680" yWindow="1815" windowWidth="29040" windowHeight="15720" tabRatio="500"/>
   </ns0:bookViews>
   <ns0:sheets>
     <ns0:sheet name="Weigh-in" sheetId="1" r:id="rId1"/>
@@ -177,7 +171,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
@@ -866,7 +860,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1455,7 +1449,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
